--- a/sweat-brand/David_Tickets_Business_Plan_v6_phased.xlsx
+++ b/sweat-brand/David_Tickets_Business_Plan_v6_phased.xlsx
@@ -4017,7 +4017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D14"/>
+  <dimension ref="B2:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -4039,133 +4039,140 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="16" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>The split reallocates v5.1: less on B2B marketing, more on product, because the AI and data roadmap needs more build than v5.1 assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>What it is</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Team ahead of revenue</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>435000</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>The booking team and directors from the raise until trading revenue carries them (months 6-14).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tour float</t>
+          <t>Team ahead of revenue</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>215000</v>
+        <v>380000</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Show marketing is spent before the show settles. This is the working capital that lets us front it.</t>
+          <t>The booking team and directors from the raise until trading revenue carries them (months 6-14).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Market entry</t>
+          <t>Product, data and AI</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>190000</v>
+        <v>250000</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>The agent conferences - Eurosonic, The Great Escape, ADE, Reeperbahn - and B2B marketing, monthly.</t>
+          <t>Routing, the data learning that improves every tour, and the automation phases 2 and 3 depend on. This is above the v5.1 development assumption: the build is running but is a long way from finished.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Tour float</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>100000</v>
+        <v>160000</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Retained development and hosting, and the phase 2 build that puts artist teams in the product.</t>
+          <t>Show marketing is spent before the show settles. This is the working capital that lets us front it.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
+          <t>Market entry</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>The agent conferences - Eurosonic, The Great Escape, ADE, Reeperbahn - and B2B marketing, monthly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Licences and setup</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C11" s="14" t="n">
         <v>60000</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>FCA payments opinion, contract templates, VAT and tax registration per territory.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C12" s="17" t="n">
         <v>1000000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Peak cash requirement</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>515571</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Month 12 of the plan, before any seed money. Cash turns positive month 14.</t>
-        </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>Peak cash requirement</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>515571</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Month 12 of the plan, before any seed money. Cash turns positive month 14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
           <t>Headroom over the plan</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C15" s="14" t="n">
         <v>484429</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>A slower ramp does not become a second raise.</t>
         </is>
